--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -2373,10 +2373,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117735033</v>
+        <v>117735025</v>
       </c>
       <c r="B17" t="n">
-        <v>108703</v>
+        <v>97858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2385,38 +2385,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>727919</v>
+        <v>727980</v>
       </c>
       <c r="R17" t="n">
-        <v>6408129</v>
+        <v>6408170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2480,7 +2489,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117735025</v>
+        <v>117735030</v>
       </c>
       <c r="B18" t="n">
         <v>97858</v>
@@ -2515,7 +2524,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2529,13 +2538,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>727980</v>
+        <v>727945</v>
       </c>
       <c r="R18" t="n">
-        <v>6408170</v>
+        <v>6408143</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2596,10 +2605,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117735030</v>
+        <v>117735057</v>
       </c>
       <c r="B19" t="n">
-        <v>97858</v>
+        <v>108703</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2608,50 +2617,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>727945</v>
+        <v>727917</v>
       </c>
       <c r="R19" t="n">
-        <v>6408143</v>
+        <v>6408255</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117735057</v>
+        <v>117735034</v>
       </c>
       <c r="B20" t="n">
         <v>108703</v>
@@ -2748,14 +2748,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>727917</v>
+        <v>727901</v>
       </c>
       <c r="R20" t="n">
-        <v>6408255</v>
+        <v>6408095</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2819,7 +2819,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117735034</v>
+        <v>117735033</v>
       </c>
       <c r="B21" t="n">
         <v>108703</v>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>727901</v>
+        <v>727919</v>
       </c>
       <c r="R21" t="n">
-        <v>6408095</v>
+        <v>6408129</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117735055</v>
+        <v>117735087</v>
       </c>
       <c r="B35" t="n">
-        <v>97858</v>
+        <v>108703</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4369,55 +4369,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>727917</v>
+        <v>728013</v>
       </c>
       <c r="R35" t="n">
-        <v>6408255</v>
+        <v>6408389</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4447,6 +4433,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4478,7 +4469,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117735087</v>
+        <v>117735069</v>
       </c>
       <c r="B36" t="n">
         <v>108703</v>
@@ -4518,13 +4509,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>728013</v>
+        <v>727953</v>
       </c>
       <c r="R36" t="n">
-        <v>6408389</v>
+        <v>6408340</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4554,11 +4545,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>spridd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4590,10 +4576,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117735069</v>
+        <v>117735055</v>
       </c>
       <c r="B37" t="n">
-        <v>108703</v>
+        <v>97858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4602,38 +4588,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>727953</v>
+        <v>727917</v>
       </c>
       <c r="R37" t="n">
-        <v>6408340</v>
+        <v>6408255</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117735105</v>
+        <v>117735081</v>
       </c>
       <c r="B38" t="n">
-        <v>57963</v>
+        <v>105484</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4709,50 +4709,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103044</v>
+        <v>220785</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>727945</v>
+        <v>728000</v>
       </c>
       <c r="R38" t="n">
-        <v>6408143</v>
+        <v>6408420</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4792,6 +4783,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4808,10 +4804,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117735081</v>
+        <v>117735105</v>
       </c>
       <c r="B39" t="n">
-        <v>105484</v>
+        <v>57963</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4820,41 +4816,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220785</v>
+        <v>103044</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>728000</v>
+        <v>727945</v>
       </c>
       <c r="R39" t="n">
-        <v>6408420</v>
+        <v>6408143</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4894,11 +4899,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Barrblandskog, äldre.</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -2373,10 +2373,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117735025</v>
+        <v>117735053</v>
       </c>
       <c r="B17" t="n">
-        <v>97858</v>
+        <v>108703</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2385,47 +2385,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>727980</v>
+        <v>727808</v>
       </c>
       <c r="R17" t="n">
-        <v>6408170</v>
+        <v>6408213</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117735030</v>
+        <v>117735026</v>
       </c>
       <c r="B18" t="n">
-        <v>97858</v>
+        <v>105484</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,50 +2492,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>727945</v>
+        <v>727973</v>
       </c>
       <c r="R18" t="n">
-        <v>6408143</v>
+        <v>6408168</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2605,7 +2587,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117735057</v>
+        <v>117735075</v>
       </c>
       <c r="B19" t="n">
         <v>108703</v>
@@ -2645,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>727917</v>
+        <v>727965</v>
       </c>
       <c r="R19" t="n">
-        <v>6408255</v>
+        <v>6408410</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,7 +2694,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117735034</v>
+        <v>117735069</v>
       </c>
       <c r="B20" t="n">
         <v>108703</v>
@@ -2748,14 +2730,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>727901</v>
+        <v>727953</v>
       </c>
       <c r="R20" t="n">
-        <v>6408095</v>
+        <v>6408340</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2819,10 +2801,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117735033</v>
+        <v>117735066</v>
       </c>
       <c r="B21" t="n">
-        <v>108703</v>
+        <v>97859</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2831,41 +2813,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>727919</v>
+        <v>727950</v>
       </c>
       <c r="R21" t="n">
-        <v>6408129</v>
+        <v>6408344</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2926,10 +2917,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117735074</v>
+        <v>117735064</v>
       </c>
       <c r="B22" t="n">
-        <v>97870</v>
+        <v>108703</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2938,50 +2929,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>727960</v>
+        <v>727930</v>
       </c>
       <c r="R22" t="n">
-        <v>6408402</v>
+        <v>6408341</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3042,10 +3024,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117735043</v>
+        <v>117735025</v>
       </c>
       <c r="B23" t="n">
-        <v>108703</v>
+        <v>97858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3054,38 +3036,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>727868</v>
+        <v>727980</v>
       </c>
       <c r="R23" t="n">
-        <v>6408045</v>
+        <v>6408170</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3131,7 +3122,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Barrskog grov, gles.</t>
+          <t>Barrblandskog, äldre.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3149,10 +3140,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117735029</v>
+        <v>117735030</v>
       </c>
       <c r="B24" t="n">
-        <v>97870</v>
+        <v>97858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3165,16 +3156,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>219862</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3184,7 +3175,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3265,7 +3256,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117735032</v>
+        <v>117735028</v>
       </c>
       <c r="B25" t="n">
         <v>108703</v>
@@ -3305,13 +3296,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>727931</v>
+        <v>727945</v>
       </c>
       <c r="R25" t="n">
-        <v>6408133</v>
+        <v>6408143</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3372,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117735064</v>
+        <v>117735065</v>
       </c>
       <c r="B26" t="n">
-        <v>108703</v>
+        <v>97859</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3384,28 +3375,37 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117735062</v>
+        <v>117735087</v>
       </c>
       <c r="B27" t="n">
-        <v>97858</v>
+        <v>108703</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,45 +3491,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>727911</v>
+        <v>728013</v>
       </c>
       <c r="R27" t="n">
-        <v>6408328</v>
+        <v>6408389</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3559,6 +3555,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>spridd.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3590,10 +3591,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117735076</v>
+        <v>117735074</v>
       </c>
       <c r="B28" t="n">
-        <v>97859</v>
+        <v>97870</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3606,26 +3607,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>219874</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3639,13 +3640,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>727965</v>
+        <v>727960</v>
       </c>
       <c r="R28" t="n">
-        <v>6408410</v>
+        <v>6408402</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3706,7 +3707,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117735075</v>
+        <v>117735032</v>
       </c>
       <c r="B29" t="n">
         <v>108703</v>
@@ -3742,14 +3743,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>727965</v>
+        <v>727931</v>
       </c>
       <c r="R29" t="n">
-        <v>6408410</v>
+        <v>6408133</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3813,7 +3814,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117735028</v>
+        <v>117735043</v>
       </c>
       <c r="B30" t="n">
         <v>108703</v>
@@ -3853,13 +3854,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>727945</v>
+        <v>727868</v>
       </c>
       <c r="R30" t="n">
-        <v>6408143</v>
+        <v>6408045</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3902,7 +3903,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Barrblandskog, äldre.</t>
+          <t>Barrskog grov, gles.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3920,10 +3921,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117735026</v>
+        <v>117735057</v>
       </c>
       <c r="B31" t="n">
-        <v>105484</v>
+        <v>108703</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3932,20 +3933,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3956,14 +3957,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>727973</v>
+        <v>727917</v>
       </c>
       <c r="R31" t="n">
-        <v>6408168</v>
+        <v>6408255</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4027,10 +4028,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117735060</v>
+        <v>117735055</v>
       </c>
       <c r="B32" t="n">
-        <v>97754</v>
+        <v>97858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4043,31 +4044,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4082,7 +4088,7 @@
         <v>6408255</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4143,10 +4149,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117735078</v>
+        <v>117735019</v>
       </c>
       <c r="B33" t="n">
-        <v>100097</v>
+        <v>108703</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4155,38 +4161,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>727992</v>
+        <v>728015</v>
       </c>
       <c r="R33" t="n">
-        <v>6408434</v>
+        <v>6408239</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4250,7 +4256,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117735020</v>
+        <v>117735080</v>
       </c>
       <c r="B34" t="n">
         <v>108703</v>
@@ -4286,17 +4292,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>728015</v>
+        <v>727992</v>
       </c>
       <c r="R34" t="n">
-        <v>6408239</v>
+        <v>6408434</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4326,6 +4332,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4357,10 +4368,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117735087</v>
+        <v>117735062</v>
       </c>
       <c r="B35" t="n">
-        <v>108703</v>
+        <v>97858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4369,41 +4380,45 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>728013</v>
+        <v>727911</v>
       </c>
       <c r="R35" t="n">
-        <v>6408389</v>
+        <v>6408328</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4433,11 +4448,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,7 +4479,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117735069</v>
+        <v>117735021</v>
       </c>
       <c r="B36" t="n">
         <v>108703</v>
@@ -4505,14 +4515,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>727953</v>
+        <v>727984</v>
       </c>
       <c r="R36" t="n">
-        <v>6408340</v>
+        <v>6408192</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4576,10 +4586,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117735055</v>
+        <v>117735027</v>
       </c>
       <c r="B37" t="n">
-        <v>97858</v>
+        <v>108703</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4588,52 +4598,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>727917</v>
+        <v>727973</v>
       </c>
       <c r="R37" t="n">
-        <v>6408255</v>
+        <v>6408168</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4697,10 +4693,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117735081</v>
+        <v>117735034</v>
       </c>
       <c r="B38" t="n">
-        <v>105484</v>
+        <v>108703</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4709,20 +4705,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4733,17 +4729,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>728000</v>
+        <v>727901</v>
       </c>
       <c r="R38" t="n">
-        <v>6408420</v>
+        <v>6408095</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4804,10 +4800,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117735105</v>
+        <v>117735059</v>
       </c>
       <c r="B39" t="n">
-        <v>57963</v>
+        <v>105484</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4816,50 +4812,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103044</v>
+        <v>220785</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>727945</v>
+        <v>727917</v>
       </c>
       <c r="R39" t="n">
-        <v>6408143</v>
+        <v>6408255</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4899,6 +4886,11 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4915,10 +4907,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117735053</v>
+        <v>117735070</v>
       </c>
       <c r="B40" t="n">
-        <v>108703</v>
+        <v>97754</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4927,41 +4919,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>727808</v>
+        <v>727953</v>
       </c>
       <c r="R40" t="n">
-        <v>6408213</v>
+        <v>6408340</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5022,7 +5023,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117735022</v>
+        <v>117735083</v>
       </c>
       <c r="B41" t="n">
         <v>97859</v>
@@ -5057,7 +5058,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5067,17 +5068,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>727987</v>
+        <v>728000</v>
       </c>
       <c r="R41" t="n">
-        <v>6408194</v>
+        <v>6408420</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5138,10 +5139,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117735070</v>
+        <v>117735081</v>
       </c>
       <c r="B42" t="n">
-        <v>97754</v>
+        <v>105484</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5150,50 +5151,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>727953</v>
+        <v>728000</v>
       </c>
       <c r="R42" t="n">
-        <v>6408340</v>
+        <v>6408420</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5254,10 +5246,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117735113</v>
+        <v>117735029</v>
       </c>
       <c r="B43" t="n">
-        <v>57770</v>
+        <v>97870</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5270,46 +5262,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102625</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>727917</v>
+        <v>727945</v>
       </c>
       <c r="R43" t="n">
-        <v>6408255</v>
+        <v>6408143</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5370,10 +5362,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117735024</v>
+        <v>117735060</v>
       </c>
       <c r="B44" t="n">
-        <v>97858</v>
+        <v>97754</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5386,26 +5378,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5415,17 +5407,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>727984</v>
+        <v>727917</v>
       </c>
       <c r="R44" t="n">
-        <v>6408192</v>
+        <v>6408255</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5455,11 +5447,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Även 6 fjolårsståndare.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5491,7 +5478,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117735027</v>
+        <v>117735072</v>
       </c>
       <c r="B45" t="n">
         <v>108703</v>
@@ -5527,14 +5514,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>727973</v>
+        <v>727966</v>
       </c>
       <c r="R45" t="n">
-        <v>6408168</v>
+        <v>6408355</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5598,10 +5585,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117735059</v>
+        <v>117735024</v>
       </c>
       <c r="B46" t="n">
-        <v>105484</v>
+        <v>97858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5610,41 +5597,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>727917</v>
+        <v>727984</v>
       </c>
       <c r="R46" t="n">
-        <v>6408255</v>
+        <v>6408192</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5674,6 +5670,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Även 6 fjolårsståndare.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5705,10 +5706,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117735080</v>
+        <v>117735076</v>
       </c>
       <c r="B47" t="n">
-        <v>108703</v>
+        <v>97859</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5717,41 +5718,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>727992</v>
+        <v>727965</v>
       </c>
       <c r="R47" t="n">
-        <v>6408434</v>
+        <v>6408410</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5781,11 +5791,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5817,10 +5822,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117735109</v>
+        <v>117735078</v>
       </c>
       <c r="B48" t="n">
-        <v>57770</v>
+        <v>100097</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5833,46 +5838,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102625</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>727887</v>
+        <v>727992</v>
       </c>
       <c r="R48" t="n">
-        <v>6408067</v>
+        <v>6408434</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5933,7 +5929,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117735072</v>
+        <v>117735033</v>
       </c>
       <c r="B49" t="n">
         <v>108703</v>
@@ -5969,14 +5965,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>727966</v>
+        <v>727919</v>
       </c>
       <c r="R49" t="n">
-        <v>6408355</v>
+        <v>6408129</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6040,10 +6036,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117735065</v>
+        <v>117735105</v>
       </c>
       <c r="B50" t="n">
-        <v>97859</v>
+        <v>57963</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6056,46 +6052,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>103044</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>727930</v>
+        <v>727945</v>
       </c>
       <c r="R50" t="n">
-        <v>6408341</v>
+        <v>6408143</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6135,11 +6131,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Barrblandskog, äldre.</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6156,7 +6147,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117735066</v>
+        <v>117735022</v>
       </c>
       <c r="B51" t="n">
         <v>97859</v>
@@ -6191,7 +6182,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6201,17 +6192,17 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>727950</v>
+        <v>727987</v>
       </c>
       <c r="R51" t="n">
-        <v>6408344</v>
+        <v>6408194</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6272,10 +6263,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117735083</v>
+        <v>117735113</v>
       </c>
       <c r="B52" t="n">
-        <v>97859</v>
+        <v>57770</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6288,31 +6279,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>102625</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6321,13 +6312,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>728000</v>
+        <v>727917</v>
       </c>
       <c r="R52" t="n">
-        <v>6408420</v>
+        <v>6408255</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6388,10 +6379,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117735021</v>
+        <v>117735109</v>
       </c>
       <c r="B53" t="n">
-        <v>108703</v>
+        <v>57770</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6400,41 +6391,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220299</v>
+        <v>102625</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>727984</v>
+        <v>727887</v>
       </c>
       <c r="R53" t="n">
-        <v>6408192</v>
+        <v>6408067</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -2373,10 +2373,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117735053</v>
+        <v>117735072</v>
       </c>
       <c r="B17" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>727808</v>
+        <v>727966</v>
       </c>
       <c r="R17" t="n">
-        <v>6408213</v>
+        <v>6408355</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117735026</v>
+        <v>117735033</v>
       </c>
       <c r="B18" t="n">
-        <v>105484</v>
+        <v>108705</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,20 +2492,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>727973</v>
+        <v>727919</v>
       </c>
       <c r="R18" t="n">
-        <v>6408168</v>
+        <v>6408129</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,10 +2587,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117735075</v>
+        <v>117735064</v>
       </c>
       <c r="B19" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2627,13 +2627,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>727965</v>
+        <v>727930</v>
       </c>
       <c r="R19" t="n">
-        <v>6408410</v>
+        <v>6408341</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117735069</v>
+        <v>117735081</v>
       </c>
       <c r="B20" t="n">
-        <v>108703</v>
+        <v>105486</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,20 +2706,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>727953</v>
+        <v>728000</v>
       </c>
       <c r="R20" t="n">
-        <v>6408340</v>
+        <v>6408420</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2801,10 +2801,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117735066</v>
+        <v>117735019</v>
       </c>
       <c r="B21" t="n">
-        <v>97859</v>
+        <v>108705</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2813,50 +2813,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>727950</v>
+        <v>728015</v>
       </c>
       <c r="R21" t="n">
-        <v>6408344</v>
+        <v>6408239</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2917,10 +2908,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117735064</v>
+        <v>117735043</v>
       </c>
       <c r="B22" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2953,17 +2944,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>727930</v>
+        <v>727868</v>
       </c>
       <c r="R22" t="n">
-        <v>6408341</v>
+        <v>6408045</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3006,7 +2997,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Barrblandskog, äldre.</t>
+          <t>Barrskog grov, gles.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3024,10 +3015,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117735025</v>
+        <v>117735055</v>
       </c>
       <c r="B23" t="n">
-        <v>97858</v>
+        <v>97860</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3059,7 +3050,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3067,16 +3058,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>727980</v>
+        <v>727917</v>
       </c>
       <c r="R23" t="n">
-        <v>6408170</v>
+        <v>6408255</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3140,10 +3136,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117735030</v>
+        <v>117735083</v>
       </c>
       <c r="B24" t="n">
-        <v>97858</v>
+        <v>97861</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,26 +3152,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3185,17 +3181,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>727945</v>
+        <v>728000</v>
       </c>
       <c r="R24" t="n">
-        <v>6408143</v>
+        <v>6408420</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3256,10 +3252,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117735028</v>
+        <v>117735087</v>
       </c>
       <c r="B25" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,17 +3288,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>727945</v>
+        <v>728013</v>
       </c>
       <c r="R25" t="n">
-        <v>6408143</v>
+        <v>6408389</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3332,6 +3328,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>spridd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,10 +3364,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117735065</v>
+        <v>117735105</v>
       </c>
       <c r="B26" t="n">
-        <v>97859</v>
+        <v>57964</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,46 +3380,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219847</v>
+        <v>103044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>727930</v>
+        <v>727945</v>
       </c>
       <c r="R26" t="n">
-        <v>6408341</v>
+        <v>6408143</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3458,11 +3459,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Barrblandskog, äldre.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3479,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117735087</v>
+        <v>117735066</v>
       </c>
       <c r="B27" t="n">
-        <v>108703</v>
+        <v>97861</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,41 +3487,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>728013</v>
+        <v>727950</v>
       </c>
       <c r="R27" t="n">
-        <v>6408389</v>
+        <v>6408344</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3555,11 +3560,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>spridd.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,10 +3591,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117735074</v>
+        <v>117735078</v>
       </c>
       <c r="B28" t="n">
-        <v>97870</v>
+        <v>100099</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3607,43 +3607,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>727960</v>
+        <v>727992</v>
       </c>
       <c r="R28" t="n">
-        <v>6408402</v>
+        <v>6408434</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3707,10 +3698,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117735032</v>
+        <v>117735026</v>
       </c>
       <c r="B29" t="n">
-        <v>108703</v>
+        <v>105486</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3719,20 +3710,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3747,10 +3738,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>727931</v>
+        <v>727973</v>
       </c>
       <c r="R29" t="n">
-        <v>6408133</v>
+        <v>6408168</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3814,10 +3805,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117735043</v>
+        <v>117735029</v>
       </c>
       <c r="B30" t="n">
-        <v>108703</v>
+        <v>97872</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3826,41 +3817,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>219874</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>727868</v>
+        <v>727945</v>
       </c>
       <c r="R30" t="n">
-        <v>6408045</v>
+        <v>6408143</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Barrskog grov, gles.</t>
+          <t>Barrblandskog, äldre.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117735057</v>
+        <v>117735032</v>
       </c>
       <c r="B31" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3957,14 +3957,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>727917</v>
+        <v>727931</v>
       </c>
       <c r="R31" t="n">
-        <v>6408255</v>
+        <v>6408133</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4028,10 +4028,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117735055</v>
+        <v>117735057</v>
       </c>
       <c r="B32" t="n">
-        <v>97858</v>
+        <v>108705</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4040,42 +4040,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
@@ -4149,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117735019</v>
+        <v>117735028</v>
       </c>
       <c r="B33" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4189,13 +4175,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>728015</v>
+        <v>727945</v>
       </c>
       <c r="R33" t="n">
-        <v>6408239</v>
+        <v>6408143</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4256,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117735080</v>
+        <v>117735022</v>
       </c>
       <c r="B34" t="n">
-        <v>108703</v>
+        <v>97861</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4268,41 +4254,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>727992</v>
+        <v>727987</v>
       </c>
       <c r="R34" t="n">
-        <v>6408434</v>
+        <v>6408194</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4332,11 +4327,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4368,10 +4358,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117735062</v>
+        <v>117735076</v>
       </c>
       <c r="B35" t="n">
-        <v>97858</v>
+        <v>97861</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4384,26 +4374,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4412,13 +4407,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>727911</v>
+        <v>727965</v>
       </c>
       <c r="R35" t="n">
-        <v>6408328</v>
+        <v>6408410</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4479,10 +4474,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117735021</v>
+        <v>117735030</v>
       </c>
       <c r="B36" t="n">
-        <v>108703</v>
+        <v>97860</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4491,41 +4486,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>727984</v>
+        <v>727945</v>
       </c>
       <c r="R36" t="n">
-        <v>6408192</v>
+        <v>6408143</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4586,10 +4590,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117735027</v>
+        <v>117735074</v>
       </c>
       <c r="B37" t="n">
-        <v>108703</v>
+        <v>97872</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4598,38 +4602,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220299</v>
+        <v>219874</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>727973</v>
+        <v>727960</v>
       </c>
       <c r="R37" t="n">
-        <v>6408168</v>
+        <v>6408402</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4693,10 +4706,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117735034</v>
+        <v>117735113</v>
       </c>
       <c r="B38" t="n">
-        <v>108703</v>
+        <v>57771</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4705,41 +4718,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220299</v>
+        <v>102625</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>727901</v>
+        <v>727917</v>
       </c>
       <c r="R38" t="n">
-        <v>6408095</v>
+        <v>6408255</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4800,10 +4822,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117735059</v>
+        <v>117735034</v>
       </c>
       <c r="B39" t="n">
-        <v>105484</v>
+        <v>108705</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4812,20 +4834,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4836,17 +4858,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>727917</v>
+        <v>727901</v>
       </c>
       <c r="R39" t="n">
-        <v>6408255</v>
+        <v>6408095</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4907,10 +4929,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117735070</v>
+        <v>117735069</v>
       </c>
       <c r="B40" t="n">
-        <v>97754</v>
+        <v>108705</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4919,37 +4941,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
@@ -4962,7 +4975,7 @@
         <v>6408340</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5023,10 +5036,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117735083</v>
+        <v>117735065</v>
       </c>
       <c r="B41" t="n">
-        <v>97859</v>
+        <v>97861</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,7 +5071,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5072,10 +5085,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>728000</v>
+        <v>727930</v>
       </c>
       <c r="R41" t="n">
-        <v>6408420</v>
+        <v>6408341</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5139,10 +5152,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117735081</v>
+        <v>117735062</v>
       </c>
       <c r="B42" t="n">
-        <v>105484</v>
+        <v>97860</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5151,41 +5164,45 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>728000</v>
+        <v>727911</v>
       </c>
       <c r="R42" t="n">
-        <v>6408420</v>
+        <v>6408328</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5246,10 +5263,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117735029</v>
+        <v>117735070</v>
       </c>
       <c r="B43" t="n">
-        <v>97870</v>
+        <v>97756</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5262,26 +5279,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>223591</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5291,17 +5308,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>727945</v>
+        <v>727953</v>
       </c>
       <c r="R43" t="n">
-        <v>6408143</v>
+        <v>6408340</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5362,10 +5379,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117735060</v>
+        <v>117735053</v>
       </c>
       <c r="B44" t="n">
-        <v>97754</v>
+        <v>108705</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5374,50 +5391,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>727917</v>
+        <v>727808</v>
       </c>
       <c r="R44" t="n">
-        <v>6408255</v>
+        <v>6408213</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5478,10 +5486,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117735072</v>
+        <v>117735027</v>
       </c>
       <c r="B45" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5514,14 +5522,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>727966</v>
+        <v>727973</v>
       </c>
       <c r="R45" t="n">
-        <v>6408355</v>
+        <v>6408168</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5585,10 +5593,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117735024</v>
+        <v>117735109</v>
       </c>
       <c r="B46" t="n">
-        <v>97858</v>
+        <v>57771</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5601,31 +5609,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219862</v>
+        <v>102625</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5634,13 +5642,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>727984</v>
+        <v>727887</v>
       </c>
       <c r="R46" t="n">
-        <v>6408192</v>
+        <v>6408067</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5670,11 +5678,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Även 6 fjolårsståndare.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5706,10 +5709,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117735076</v>
+        <v>117735024</v>
       </c>
       <c r="B47" t="n">
-        <v>97859</v>
+        <v>97860</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5722,26 +5725,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5751,17 +5754,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>727965</v>
+        <v>727984</v>
       </c>
       <c r="R47" t="n">
-        <v>6408410</v>
+        <v>6408192</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5791,6 +5794,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Även 6 fjolårsståndare.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5822,10 +5830,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117735078</v>
+        <v>117735075</v>
       </c>
       <c r="B48" t="n">
-        <v>100097</v>
+        <v>108705</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5834,25 +5842,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5862,10 +5870,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>727992</v>
+        <v>727965</v>
       </c>
       <c r="R48" t="n">
-        <v>6408434</v>
+        <v>6408410</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5929,10 +5937,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117735033</v>
+        <v>117735021</v>
       </c>
       <c r="B49" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5969,10 +5977,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>727919</v>
+        <v>727984</v>
       </c>
       <c r="R49" t="n">
-        <v>6408129</v>
+        <v>6408192</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6036,10 +6044,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117735105</v>
+        <v>117735080</v>
       </c>
       <c r="B50" t="n">
-        <v>57963</v>
+        <v>108705</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6048,50 +6056,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103044</v>
+        <v>220299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>727945</v>
+        <v>727992</v>
       </c>
       <c r="R50" t="n">
-        <v>6408143</v>
+        <v>6408434</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6123,6 +6122,11 @@
           <t>2024-05-26</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6131,6 +6135,11 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6147,10 +6156,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117735022</v>
+        <v>117735060</v>
       </c>
       <c r="B51" t="n">
-        <v>97859</v>
+        <v>97756</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6163,26 +6172,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6192,17 +6201,17 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>727987</v>
+        <v>727917</v>
       </c>
       <c r="R51" t="n">
-        <v>6408194</v>
+        <v>6408255</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6263,10 +6272,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117735113</v>
+        <v>117735059</v>
       </c>
       <c r="B52" t="n">
-        <v>57770</v>
+        <v>105486</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6275,37 +6284,28 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102625</v>
+        <v>220785</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
@@ -6318,7 +6318,7 @@
         <v>6408255</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6379,10 +6379,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117735109</v>
+        <v>117735025</v>
       </c>
       <c r="B53" t="n">
-        <v>57770</v>
+        <v>97860</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6395,31 +6395,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102625</v>
+        <v>219862</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6428,13 +6428,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>727887</v>
+        <v>727980</v>
       </c>
       <c r="R53" t="n">
-        <v>6408067</v>
+        <v>6408170</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -3136,10 +3136,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117735083</v>
+        <v>117735087</v>
       </c>
       <c r="B24" t="n">
-        <v>97861</v>
+        <v>108705</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3148,50 +3148,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>728000</v>
+        <v>728013</v>
       </c>
       <c r="R24" t="n">
-        <v>6408420</v>
+        <v>6408389</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3221,6 +3212,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>spridd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3252,10 +3248,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117735087</v>
+        <v>117735083</v>
       </c>
       <c r="B25" t="n">
-        <v>108705</v>
+        <v>97861</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3264,41 +3260,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>728013</v>
+        <v>728000</v>
       </c>
       <c r="R25" t="n">
-        <v>6408389</v>
+        <v>6408420</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3328,11 +3333,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>spridd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -5709,10 +5709,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117735024</v>
+        <v>117735060</v>
       </c>
       <c r="B47" t="n">
-        <v>97860</v>
+        <v>97756</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5725,26 +5725,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219862</v>
+        <v>223591</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5754,17 +5754,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>727984</v>
+        <v>727917</v>
       </c>
       <c r="R47" t="n">
-        <v>6408192</v>
+        <v>6408255</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5794,11 +5794,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Även 6 fjolårsståndare.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5830,10 +5825,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117735075</v>
+        <v>117735059</v>
       </c>
       <c r="B48" t="n">
-        <v>108705</v>
+        <v>105486</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5842,20 +5837,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5870,13 +5865,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>727965</v>
+        <v>727917</v>
       </c>
       <c r="R48" t="n">
-        <v>6408410</v>
+        <v>6408255</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5937,7 +5932,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117735021</v>
+        <v>117735075</v>
       </c>
       <c r="B49" t="n">
         <v>108705</v>
@@ -5973,14 +5968,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>727984</v>
+        <v>727965</v>
       </c>
       <c r="R49" t="n">
-        <v>6408192</v>
+        <v>6408410</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6044,7 +6039,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117735080</v>
+        <v>117735021</v>
       </c>
       <c r="B50" t="n">
         <v>108705</v>
@@ -6080,17 +6075,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>727992</v>
+        <v>727984</v>
       </c>
       <c r="R50" t="n">
-        <v>6408434</v>
+        <v>6408192</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6120,11 +6115,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6156,10 +6146,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117735060</v>
+        <v>117735080</v>
       </c>
       <c r="B51" t="n">
-        <v>97756</v>
+        <v>108705</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6168,50 +6158,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>727917</v>
+        <v>727992</v>
       </c>
       <c r="R51" t="n">
-        <v>6408255</v>
+        <v>6408434</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6241,6 +6222,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6272,10 +6258,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117735059</v>
+        <v>117735024</v>
       </c>
       <c r="B52" t="n">
-        <v>105486</v>
+        <v>97860</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6284,41 +6270,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>727917</v>
+        <v>727984</v>
       </c>
       <c r="R52" t="n">
-        <v>6408255</v>
+        <v>6408192</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6348,6 +6343,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Även 6 fjolårsståndare.</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6493,6 +6493,122 @@
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128590936</v>
+      </c>
+      <c r="B54" t="n">
+        <v>86714</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mörkfjällig olivspindling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cortinarius melanotus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lärbro Lulla Vägume 1:18, Lärbro Lulla Vägume 1:18, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>727840</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6408175</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -6498,7 +6498,7 @@
         <v>128590936</v>
       </c>
       <c r="B54" t="n">
-        <v>86714</v>
+        <v>86719</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -6498,7 +6498,7 @@
         <v>128590936</v>
       </c>
       <c r="B54" t="n">
-        <v>86719</v>
+        <v>86725</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -6498,7 +6498,7 @@
         <v>128590936</v>
       </c>
       <c r="B54" t="n">
-        <v>86725</v>
+        <v>86727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -6498,7 +6498,7 @@
         <v>128590936</v>
       </c>
       <c r="B54" t="n">
-        <v>86727</v>
+        <v>86754</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -6498,7 +6498,7 @@
         <v>128590936</v>
       </c>
       <c r="B54" t="n">
-        <v>86754</v>
+        <v>86758</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -6498,7 +6498,7 @@
         <v>128590936</v>
       </c>
       <c r="B54" t="n">
-        <v>86758</v>
+        <v>86762</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -6498,7 +6498,7 @@
         <v>128590936</v>
       </c>
       <c r="B54" t="n">
-        <v>86762</v>
+        <v>86767</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -6498,7 +6498,7 @@
         <v>128590936</v>
       </c>
       <c r="B54" t="n">
-        <v>86769</v>
+        <v>86774</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -6498,7 +6498,7 @@
         <v>128590936</v>
       </c>
       <c r="B54" t="n">
-        <v>86774</v>
+        <v>86780</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88914982</v>
+        <v>88914928</v>
       </c>
       <c r="B2" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727970.1225791697</v>
+        <v>727856</v>
       </c>
       <c r="R2" t="n">
-        <v>6408353.877312707</v>
+        <v>6408028</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88914914</v>
+        <v>117735109</v>
       </c>
       <c r="B3" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>473</v>
+        <v>102625</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bon</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vägume, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727955.0370624075</v>
+        <v>727887</v>
       </c>
       <c r="R3" t="n">
-        <v>6408156.775763431</v>
+        <v>6408067</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,66 +862,75 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88914941</v>
+        <v>117735111</v>
       </c>
       <c r="B4" t="n">
-        <v>85057</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1985</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vägume, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727821.2590443381</v>
+        <v>727837</v>
       </c>
       <c r="R4" t="n">
-        <v>6408239.035422333</v>
+        <v>6408071</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,22 +957,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även i skifte mot V.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,69 +978,69 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88915008</v>
+        <v>117735036</v>
       </c>
       <c r="B5" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vägume, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727946.7649839957</v>
+        <v>727898</v>
       </c>
       <c r="R5" t="n">
-        <v>6408331.165143142</v>
+        <v>6408058</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1064,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,69 +1080,69 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88914937</v>
+        <v>117735043</v>
       </c>
       <c r="B6" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vägume, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727819.7264388307</v>
+        <v>727868</v>
       </c>
       <c r="R6" t="n">
-        <v>6408228.253989087</v>
+        <v>6408045</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1166,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,69 +1182,78 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrskog grov, gles.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88914986</v>
+        <v>128588715</v>
       </c>
       <c r="B7" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vägume, Gtl</t>
+          <t>Lärbro Stora Vägume 1:56, Lärbro Stora Vägume 1:56, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>727979.0203550598</v>
+        <v>727758</v>
       </c>
       <c r="R7" t="n">
-        <v>6408177.920043283</v>
+        <v>6408248</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1277,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,12 +1307,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1350,12 +1322,7 @@
         <v>88914956</v>
       </c>
       <c r="B8" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,12 +1339,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727842.0977040761</v>
+        <v>727842</v>
       </c>
       <c r="R8" t="n">
-        <v>6408135.94116712</v>
+        <v>6408136</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,19 +1387,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1416,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88914987</v>
+        <v>88914957</v>
       </c>
       <c r="B9" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>727951.1269571995</v>
+        <v>727909</v>
       </c>
       <c r="R9" t="n">
-        <v>6408150.13730589</v>
+        <v>6408075</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1532,19 +1484,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88914984</v>
+        <v>88914914</v>
       </c>
       <c r="B10" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1524,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>473</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>727926.8830894312</v>
+        <v>727955</v>
       </c>
       <c r="R10" t="n">
-        <v>6408303.837373495</v>
+        <v>6408157</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1644,19 +1581,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1610,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>88914927</v>
+        <v>88914941</v>
       </c>
       <c r="B11" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>1985</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>727950.1796247934</v>
+        <v>727821</v>
       </c>
       <c r="R11" t="n">
-        <v>6408147.944654626</v>
+        <v>6408239</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1756,19 +1678,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,12 +1710,7 @@
         <v>88914942</v>
       </c>
       <c r="B12" t="n">
-        <v>85057</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>727899.8343659046</v>
+        <v>727900</v>
       </c>
       <c r="R12" t="n">
-        <v>6408109.799568709</v>
+        <v>6408110</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1868,19 +1775,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,53 +1804,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>88914983</v>
+        <v>128590936</v>
       </c>
       <c r="B13" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vägume, Gtl</t>
+          <t>Lärbro Lulla Vägume 1:18, Lärbro Lulla Vägume 1:18, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727954.150870309</v>
+        <v>727840</v>
       </c>
       <c r="R13" t="n">
-        <v>6408333.187741138</v>
+        <v>6408175</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,22 +1878,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,27 +1908,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>88914985</v>
+        <v>128588504</v>
       </c>
       <c r="B14" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,37 +1931,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vägume, Gtl</t>
+          <t>Lärbro Stora Vägume 1:56, Lärbro Stora Vägume 1:56, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>727819.7867967293</v>
+        <v>727758</v>
       </c>
       <c r="R14" t="n">
-        <v>6408227.187938984</v>
+        <v>6408248</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,22 +1985,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,65 +2015,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>88914973</v>
+        <v>88915008</v>
       </c>
       <c r="B15" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vägume, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>727984.9588570406</v>
+        <v>727947</v>
       </c>
       <c r="R15" t="n">
-        <v>6408441.876367286</v>
+        <v>6408331</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2207,28 +2095,17 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-10-20</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2247,56 +2124,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>88914981</v>
+        <v>128588537</v>
       </c>
       <c r="B16" t="n">
-        <v>85289</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3727</v>
+        <v>3712</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klenodspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius spectabilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vägume, Gtl</t>
+          <t>Lärbro Stora Vägume 1:56, Lärbro Stora Vägume 1:56, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>727949.0409035158</v>
+        <v>727758</v>
       </c>
       <c r="R16" t="n">
-        <v>6408309.905124355</v>
+        <v>6408248</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2320,22 +2189,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,96 +2213,69 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Ungefär lika delar gran och tall. Kalkrik sand i botten. Äldre kontinuitetsskog.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117735055</v>
+        <v>88914981</v>
       </c>
       <c r="B17" t="n">
-        <v>97862</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219862</v>
+        <v>3727</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Klenodspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius spectabilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Vägume, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>727917</v>
+        <v>727949</v>
       </c>
       <c r="R17" t="n">
-        <v>6408255</v>
+        <v>6408310</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2457,12 +2299,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,38 +2313,39 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrblandskog, äldre.</t>
+          <t>Ungefär lika delar gran och tall. Kalkrik sand i botten. Äldre kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117735109</v>
+        <v>88914937</v>
       </c>
       <c r="B18" t="n">
-        <v>57773</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2510,43 +2353,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102625</v>
+        <v>3762</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Vägume, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>727887</v>
+        <v>727820</v>
       </c>
       <c r="R18" t="n">
-        <v>6408067</v>
+        <v>6408228</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2573,12 +2407,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,36 +2423,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Barrblandskog, äldre.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117735072</v>
+        <v>88914927</v>
       </c>
       <c r="B19" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,37 +2450,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Vägume, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>727966</v>
+        <v>727950</v>
       </c>
       <c r="R19" t="n">
-        <v>6408355</v>
+        <v>6408148</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2680,12 +2504,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,74 +2520,67 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Barrblandskog, äldre.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117735081</v>
+        <v>88914973</v>
       </c>
       <c r="B20" t="n">
-        <v>105489</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220785</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Vägume, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>728000</v>
+        <v>727985</v>
       </c>
       <c r="R20" t="n">
-        <v>6408420</v>
+        <v>6408442</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2787,12 +2604,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,82 +2618,67 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Barrblandskog, äldre.</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117735065</v>
+        <v>128587763</v>
       </c>
       <c r="B21" t="n">
-        <v>97863</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro Stora Vägume 1:56, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>727930</v>
+        <v>727758</v>
       </c>
       <c r="R21" t="n">
-        <v>6408341</v>
+        <v>6408248</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2903,12 +2705,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2917,76 +2729,76 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Barrblandskog, äldre.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117735033</v>
+        <v>117735113</v>
       </c>
       <c r="B22" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>102625</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>727919</v>
+        <v>727917</v>
       </c>
       <c r="R22" t="n">
-        <v>6408129</v>
+        <v>6408255</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3047,42 +2859,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117735062</v>
+        <v>117735112</v>
       </c>
       <c r="B23" t="n">
-        <v>97862</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219862</v>
+        <v>103012</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3091,13 +2903,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>727911</v>
+        <v>727781</v>
       </c>
       <c r="R23" t="n">
-        <v>6408328</v>
+        <v>6408196</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3127,6 +2939,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Även i skifte mot V.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,53 +2975,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117735053</v>
+        <v>117735105</v>
       </c>
       <c r="B24" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220299</v>
+        <v>103044</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>727808</v>
+        <v>727945</v>
       </c>
       <c r="R24" t="n">
-        <v>6408213</v>
+        <v>6408143</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3244,11 +3065,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrblandskog, äldre.</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3265,15 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117735078</v>
+        <v>128588096</v>
       </c>
       <c r="B25" t="n">
-        <v>100101</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,37 +3092,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Vägume, Vägume, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>727992</v>
+        <v>727751</v>
       </c>
       <c r="R25" t="n">
-        <v>6408434</v>
+        <v>6408254</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3335,12 +3155,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3351,74 +3181,73 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Barrblandskog, äldre.</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Henrik Johansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Henrik Johansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117735043</v>
+        <v>128588159</v>
       </c>
       <c r="B26" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Vägume, Vägume, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>727868</v>
+        <v>727751</v>
       </c>
       <c r="R26" t="n">
-        <v>6408045</v>
+        <v>6408254</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3442,12 +3271,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3458,74 +3297,73 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Barrskog grov, gles.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Henrik Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Henrik Johansson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117735059</v>
+        <v>128588776</v>
       </c>
       <c r="B27" t="n">
-        <v>105489</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro Stora Vägume 1:56, Lärbro Stora Vägume 1:56, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>727917</v>
+        <v>727758</v>
       </c>
       <c r="R27" t="n">
-        <v>6408255</v>
+        <v>6408248</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3549,12 +3387,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3565,36 +3413,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Barrblandskog, äldre.</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117735024</v>
+        <v>117735022</v>
       </c>
       <c r="B28" t="n">
-        <v>97862</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,26 +3440,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3635,10 +3473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>727984</v>
+        <v>727987</v>
       </c>
       <c r="R28" t="n">
-        <v>6408192</v>
+        <v>6408194</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3671,11 +3509,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Även 6 fjolårsståndare.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3707,53 +3540,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117735087</v>
+        <v>117735065</v>
       </c>
       <c r="B29" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>728013</v>
+        <v>727930</v>
       </c>
       <c r="R29" t="n">
-        <v>6408389</v>
+        <v>6408341</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3783,11 +3620,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>spridd.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3819,53 +3651,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117735027</v>
+        <v>117735066</v>
       </c>
       <c r="B30" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>727973</v>
+        <v>727950</v>
       </c>
       <c r="R30" t="n">
-        <v>6408168</v>
+        <v>6408344</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3926,53 +3762,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117735069</v>
+        <v>117735076</v>
       </c>
       <c r="B31" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>727953</v>
+        <v>727965</v>
       </c>
       <c r="R31" t="n">
-        <v>6408340</v>
+        <v>6408410</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4033,53 +3873,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117735020</v>
+        <v>117735083</v>
       </c>
       <c r="B32" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>728015</v>
+        <v>728000</v>
       </c>
       <c r="R32" t="n">
-        <v>6408239</v>
+        <v>6408420</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4140,50 +3984,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117735034</v>
+        <v>117735024</v>
       </c>
       <c r="B33" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>727901</v>
+        <v>727984</v>
       </c>
       <c r="R33" t="n">
-        <v>6408095</v>
+        <v>6408192</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4216,6 +4064,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Även 6 fjolårsståndare.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4247,15 +4100,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117735060</v>
+        <v>117735025</v>
       </c>
       <c r="B34" t="n">
-        <v>97758</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,26 +4111,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223591</v>
+        <v>219862</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4292,17 +4140,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>727917</v>
+        <v>727980</v>
       </c>
       <c r="R34" t="n">
-        <v>6408255</v>
+        <v>6408170</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4366,12 +4214,7 @@
         <v>117735030</v>
       </c>
       <c r="B35" t="n">
-        <v>97862</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4479,50 +4322,59 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117735021</v>
+        <v>117735055</v>
       </c>
       <c r="B36" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>727984</v>
+        <v>727917</v>
       </c>
       <c r="R36" t="n">
-        <v>6408192</v>
+        <v>6408255</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,15 +4438,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117735029</v>
+        <v>117735062</v>
       </c>
       <c r="B37" t="n">
-        <v>97874</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4602,16 +4449,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>219862</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4624,24 +4471,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>727945</v>
+        <v>727911</v>
       </c>
       <c r="R37" t="n">
-        <v>6408143</v>
+        <v>6408328</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4702,15 +4544,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117735022</v>
+        <v>117735018</v>
       </c>
       <c r="B38" t="n">
-        <v>97863</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4718,26 +4555,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219847</v>
+        <v>219864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4751,10 +4588,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>727987</v>
+        <v>728062</v>
       </c>
       <c r="R38" t="n">
-        <v>6408194</v>
+        <v>6408286</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4800,7 +4637,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Barrblandskog, äldre.</t>
+          <t>Kraftledningsgata.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4818,15 +4655,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117735113</v>
+        <v>117735029</v>
       </c>
       <c r="B39" t="n">
-        <v>57773</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4834,46 +4666,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102625</v>
+        <v>219874</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>727917</v>
+        <v>727945</v>
       </c>
       <c r="R39" t="n">
-        <v>6408255</v>
+        <v>6408143</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4934,53 +4766,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117735080</v>
+        <v>117735074</v>
       </c>
       <c r="B40" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220299</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>727992</v>
+        <v>727960</v>
       </c>
       <c r="R40" t="n">
-        <v>6408434</v>
+        <v>6408402</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5010,11 +4846,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-05-26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5046,15 +4877,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117735064</v>
+        <v>117735015</v>
       </c>
       <c r="B41" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5082,17 +4908,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>727930</v>
+        <v>728070</v>
       </c>
       <c r="R41" t="n">
-        <v>6408341</v>
+        <v>6408300</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5135,7 +4961,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Barrblandskog, äldre.</t>
+          <t>Kraftledningsgata.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5153,62 +4979,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117735070</v>
+        <v>117735017</v>
       </c>
       <c r="B42" t="n">
-        <v>97758</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>727953</v>
+        <v>728062</v>
       </c>
       <c r="R42" t="n">
-        <v>6408340</v>
+        <v>6408286</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5251,7 +5063,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Barrblandskog, äldre.</t>
+          <t>Kraftledningsgata.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5269,62 +5081,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117735083</v>
+        <v>117735019</v>
       </c>
       <c r="B43" t="n">
-        <v>97863</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>728000</v>
+        <v>728015</v>
       </c>
       <c r="R43" t="n">
-        <v>6408420</v>
+        <v>6408239</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5385,59 +5183,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117735025</v>
+        <v>117735021</v>
       </c>
       <c r="B44" t="n">
-        <v>97862</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>727980</v>
+        <v>727984</v>
       </c>
       <c r="R44" t="n">
-        <v>6408170</v>
+        <v>6408192</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5501,62 +5285,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117735066</v>
+        <v>117735027</v>
       </c>
       <c r="B45" t="n">
-        <v>97863</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>727950</v>
+        <v>727973</v>
       </c>
       <c r="R45" t="n">
-        <v>6408344</v>
+        <v>6408168</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5617,62 +5387,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117735074</v>
+        <v>117735028</v>
       </c>
       <c r="B46" t="n">
-        <v>97874</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219874</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>727960</v>
+        <v>727945</v>
       </c>
       <c r="R46" t="n">
-        <v>6408402</v>
+        <v>6408143</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5733,62 +5489,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117735076</v>
+        <v>117735032</v>
       </c>
       <c r="B47" t="n">
-        <v>97863</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>727965</v>
+        <v>727931</v>
       </c>
       <c r="R47" t="n">
-        <v>6408410</v>
+        <v>6408133</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5849,15 +5591,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117735075</v>
+        <v>117735033</v>
       </c>
       <c r="B48" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5885,14 +5622,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>727965</v>
+        <v>727919</v>
       </c>
       <c r="R48" t="n">
-        <v>6408410</v>
+        <v>6408129</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5956,32 +5693,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117735026</v>
+        <v>117735034</v>
       </c>
       <c r="B49" t="n">
-        <v>105489</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5996,10 +5728,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>727973</v>
+        <v>727901</v>
       </c>
       <c r="R49" t="n">
-        <v>6408168</v>
+        <v>6408095</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6063,15 +5795,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117735032</v>
+        <v>117735052</v>
       </c>
       <c r="B50" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6099,14 +5826,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>727931</v>
+        <v>727781</v>
       </c>
       <c r="R50" t="n">
-        <v>6408133</v>
+        <v>6408196</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6170,62 +5897,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117735105</v>
+        <v>117735053</v>
       </c>
       <c r="B51" t="n">
-        <v>57966</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103044</v>
+        <v>220299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>727945</v>
+        <v>727808</v>
       </c>
       <c r="R51" t="n">
-        <v>6408143</v>
+        <v>6408213</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6265,6 +5978,11 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6284,12 +6002,7 @@
         <v>117735057</v>
       </c>
       <c r="B52" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6388,15 +6101,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117735028</v>
+        <v>117735064</v>
       </c>
       <c r="B53" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6424,17 +6132,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>727945</v>
+        <v>727930</v>
       </c>
       <c r="R53" t="n">
-        <v>6408143</v>
+        <v>6408341</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6495,54 +6203,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128590936</v>
+        <v>117735069</v>
       </c>
       <c r="B54" t="n">
-        <v>86780</v>
+        <v>110078</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1985</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lärbro Lulla Vägume 1:18, Lärbro Lulla Vägume 1:18, Gtl</t>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>727840</v>
+        <v>727953</v>
       </c>
       <c r="R54" t="n">
-        <v>6408175</v>
+        <v>6408340</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6569,22 +6268,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:46</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:46</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6595,19 +6284,1872 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>117735072</v>
+      </c>
+      <c r="B55" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>727966</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6408355</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>117735075</v>
+      </c>
+      <c r="B56" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>727965</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6408410</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>117735080</v>
+      </c>
+      <c r="B57" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>727992</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6408434</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>117735087</v>
+      </c>
+      <c r="B58" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>728013</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6408389</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>spridd.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>117735026</v>
+      </c>
+      <c r="B59" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lärbro, Lilla Vägume 1:8 (4) S-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>727973</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6408168</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>117735059</v>
+      </c>
+      <c r="B60" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>727917</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6408255</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>117735081</v>
+      </c>
+      <c r="B61" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>728000</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6408420</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>117735078</v>
+      </c>
+      <c r="B62" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>727992</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6408434</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>117735051</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>727792</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6408177</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre. I dike.</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>117735060</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>727917</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6408255</v>
+      </c>
+      <c r="S64" t="n">
+        <v>9</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>117735070</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lärbro, Lilla Vägume 1:8 (4) N-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>727953</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6408340</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Barrblandskog, äldre.</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>88914982</v>
+      </c>
+      <c r="B66" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Vägume, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>727970</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6408354</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>88914983</v>
+      </c>
+      <c r="B67" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Vägume, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>727954</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6408333</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>88914984</v>
+      </c>
+      <c r="B68" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Vägume, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>727927</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6408304</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>88914985</v>
+      </c>
+      <c r="B69" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Vägume, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>727820</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6408227</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>88914986</v>
+      </c>
+      <c r="B70" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Vägume, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>727979</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6408178</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>88914987</v>
+      </c>
+      <c r="B71" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Vägume, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>727951</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6408150</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128588095</v>
+      </c>
+      <c r="B72" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lärbro Stora Vägume 1:56, Lärbro Stora Vägume 1:56, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>727758</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6408248</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
           <t>Cecilia Nygren</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
+      <c r="AX72" t="inlineStr">
         <is>
           <t>Cecilia Nygren</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588715</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914956</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914957</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914914</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914941</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914942</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128590936</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588504</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88915008</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588537</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914981</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1908,6 +1968,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914937</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2005,6 +2070,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914927</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914928</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914973</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2314,6 +2394,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128587763</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2425,6 +2510,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735109</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2536,6 +2626,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735113</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2652,6 +2747,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735111</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2768,6 +2868,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735112</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2874,6 +2979,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735105</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2990,6 +3100,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588096</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3106,6 +3221,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588159</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3222,6 +3342,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588776</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3333,6 +3458,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735022</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3444,6 +3574,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735065</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3555,6 +3690,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735066</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3666,6 +3806,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735076</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3777,6 +3922,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735083</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3893,6 +4043,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735024</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4004,6 +4159,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4115,6 +4275,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735030</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4231,6 +4396,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735055</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4337,6 +4507,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735062</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4448,6 +4623,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735018</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4559,6 +4739,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735029</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4670,6 +4855,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735074</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4772,6 +4962,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735015</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4874,6 +5069,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735017</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4976,6 +5176,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735019</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5078,6 +5283,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735021</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5180,6 +5390,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735027</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5282,6 +5497,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735028</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5384,6 +5604,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735032</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5486,6 +5711,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735033</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5588,6 +5818,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735034</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5690,6 +5925,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735036</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5792,6 +6032,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735043</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5894,6 +6139,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735052</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5996,6 +6246,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735053</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6098,6 +6353,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735057</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6200,6 +6460,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735064</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6302,6 +6567,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735069</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6404,6 +6674,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735072</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6506,6 +6781,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735075</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6613,6 +6893,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735080</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6720,6 +7005,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735087</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6822,6 +7112,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735026</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6924,6 +7219,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735059</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7026,6 +7326,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735081</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7128,6 +7433,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735078</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7239,6 +7549,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735051</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7350,6 +7665,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735060</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7461,6 +7781,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117735070</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7558,6 +7883,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914982</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7655,6 +7985,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914983</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7752,6 +8087,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914984</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7849,6 +8189,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914985</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7946,6 +8291,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914986</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8043,6 +8393,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88914987</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8150,8 +8505,86 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588095</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>